--- a/Data/Excel/tech_node.xlsx
+++ b/Data/Excel/tech_node.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cube\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB062160-36AE-473D-BABB-4717C8939C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F25607F-44E4-431E-B4D5-A3FDC8CFFEB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="65">
   <si>
     <t>##var</t>
   </si>
@@ -120,75 +120,42 @@
     <t>Unlocks the building development branch.</t>
   </si>
   <si>
-    <t>仓储建设</t>
-  </si>
-  <si>
     <t>Unlocks warehouse construction.</t>
   </si>
   <si>
-    <t>定居扩建</t>
-  </si>
-  <si>
     <t>Reserved node for housing and town growth.</t>
   </si>
   <si>
-    <t>开垦农田</t>
-  </si>
-  <si>
     <t>FarmArea</t>
   </si>
   <si>
     <t>Unlocks basic crop fields.</t>
   </si>
   <si>
-    <t>花田培育</t>
-  </si>
-  <si>
     <t>Unlocks flower fields.</t>
   </si>
   <si>
-    <t>草药培育</t>
-  </si>
-  <si>
     <t>Unlocks herb fields.</t>
   </si>
   <si>
-    <t>基础工作台</t>
-  </si>
-  <si>
     <t>RecipeBasic</t>
   </si>
   <si>
     <t>Unlocks the workbench.</t>
   </si>
   <si>
-    <t>木工加工</t>
-  </si>
-  <si>
     <t>Unlocks the carpentry bench.</t>
   </si>
   <si>
-    <t>磨坊加工</t>
-  </si>
-  <si>
     <t>Unlocks the mill.</t>
   </si>
   <si>
-    <t>熔炉冶炼</t>
-  </si>
-  <si>
     <t>Unlocks the furnace.</t>
   </si>
   <si>
-    <t>铁匠锻造</t>
-  </si>
-  <si>
     <t>Unlocks the blacksmith.</t>
   </si>
   <si>
-    <t>采石技术</t>
-  </si>
-  <si>
     <t>Unlocks stone mine construction.</t>
   </si>
   <si>
@@ -202,13 +169,70 @@
   </si>
   <si>
     <t>Unlocks iron mine construction.</t>
-  </si>
-  <si>
-    <t>Assets/Arts/UI/Icons/System/House.png</t>
   </si>
   <si>
     <t>住宅</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Arts/UI/Icons/System/House.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>仓库</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>水源</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>农田</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>花田</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>草药</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>工作台</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>伐木场</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>磨坊</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>采石场</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>锻造</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>采石技术</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Arts/UI/Icons/System/farm.png</t>
+  </si>
+  <si>
+    <t>Assets/Arts/UI/Icons/System/flower.png</t>
+  </si>
+  <si>
+    <t>Assets/Arts/UI/Icons/System/lab.png</t>
+  </si>
+  <si>
+    <t>Assets/Arts/UI/Icons/System/woodland.png</t>
   </si>
 </sst>
 </file>
@@ -1362,10 +1386,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E5" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="F5">
         <v>10</v>
@@ -1403,7 +1427,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
         <v>29</v>
@@ -1424,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -1444,7 +1468,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
         <v>29</v>
@@ -1465,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L7">
         <v>1</v>
@@ -1485,10 +1509,10 @@
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="F8">
         <v>10</v>
@@ -1500,13 +1524,13 @@
         <v>30001001</v>
       </c>
       <c r="I8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L8">
         <v>1</v>
@@ -1526,10 +1550,10 @@
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="F9">
         <v>20</v>
@@ -1547,7 +1571,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="L9">
         <v>1</v>
@@ -1567,7 +1591,7 @@
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="E10" t="s">
         <v>29</v>
@@ -1588,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="L10">
         <v>1</v>
@@ -1608,10 +1632,10 @@
         <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -1623,13 +1647,13 @@
         <v>30000003</v>
       </c>
       <c r="I11" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="L11">
         <v>1</v>
@@ -1649,10 +1673,10 @@
         <v>3</v>
       </c>
       <c r="D12" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="F12">
         <v>20</v>
@@ -1670,7 +1694,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="L12">
         <v>1</v>
@@ -1690,7 +1714,7 @@
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
         <v>29</v>
@@ -1711,7 +1735,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L13">
         <v>1</v>
@@ -1731,7 +1755,7 @@
         <v>3</v>
       </c>
       <c r="D14" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E14" t="s">
         <v>29</v>
@@ -1752,7 +1776,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="L14">
         <v>1</v>
@@ -1772,7 +1796,7 @@
         <v>3</v>
       </c>
       <c r="D15" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s">
         <v>29</v>
@@ -1793,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="L15">
         <v>1</v>
@@ -1813,7 +1837,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E16" t="s">
         <v>29</v>
@@ -1834,7 +1858,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="L16">
         <v>1</v>
@@ -1854,7 +1878,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="E17" t="s">
         <v>29</v>
@@ -1875,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="L17">
         <v>1</v>
@@ -1895,7 +1919,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="E18" t="s">
         <v>29</v>
@@ -1916,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="L18">
         <v>1</v>
